--- a/grupos/5ALCM - Estadisticos 20221.xlsx
+++ b/grupos/5ALCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -116,7 +116,7 @@
     <t>MACARIO COLOHUA PERLA MARITZA</t>
   </si>
   <si>
-    <t>MARIANO ANTONIO JAQUELINE</t>
+    <t>MARIANO ANTONIO JACQUELINE</t>
   </si>
   <si>
     <t>MARTINEZ CARRERA CAROLINA</t>
@@ -218,192 +218,192 @@
     <t>ANGEL</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>JOSSELIN GUADALUPE</t>
+  </si>
+  <si>
+    <t>GENARO RAFAEL</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>BERISTAIN</t>
   </si>
   <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIA</t>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LASTRE</t>
+  </si>
+  <si>
+    <t>LARRINAGA</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TLECUILE</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
   </si>
   <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>ACEVEDO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>JOSSELIN GUADALUPE</t>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>SANTES</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>VANELY JUDITH</t>
   </si>
   <si>
     <t>JOSE ISAIAS</t>
   </si>
   <si>
-    <t>GENARO RAFAEL</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LASTRE</t>
-  </si>
-  <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TLECUILE</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>SANTES</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>VANELY JUDITH</t>
-  </si>
-  <si>
     <t>JENNIFER</t>
   </si>
   <si>
@@ -446,7 +446,7 @@
     <t>MERARY MADAY</t>
   </si>
   <si>
-    <t>JAQUELINE</t>
+    <t>JACQUELINE</t>
   </si>
   <si>
     <t>CAROLINA</t>
@@ -992,22 +992,22 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1031,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>9</v>
@@ -1040,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>10</v>
@@ -1069,13 +1069,13 @@
         <v>7</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1084,7 +1084,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1105,7 +1105,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -1120,7 +1120,7 @@
         <v>-1</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1146,22 +1146,22 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1182,7 +1182,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
         <v>7</v>
@@ -1194,10 +1194,10 @@
         <v>7</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1217,28 +1217,28 @@
         <v>8</v>
       </c>
       <c r="F7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G7">
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1262,7 +1262,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1271,7 +1271,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1300,22 +1300,22 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1336,22 +1336,22 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>7</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1377,22 +1377,22 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1413,10 +1413,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
         <v>7</v>
@@ -1425,10 +1425,10 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1454,22 +1454,22 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1490,7 +1490,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1502,10 +1502,10 @@
         <v>8</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1531,22 +1531,22 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1567,7 +1567,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1579,10 +1579,10 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1608,22 +1608,22 @@
         <v>7</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1644,10 +1644,10 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>7</v>
@@ -1656,10 +1656,10 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1685,22 +1685,22 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1721,10 +1721,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1733,10 +1733,10 @@
         <v>7</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1762,22 +1762,22 @@
         <v>10</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1839,22 +1839,22 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1875,7 +1875,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U15">
         <v>9</v>
@@ -1887,10 +1887,10 @@
         <v>7</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1916,22 +1916,22 @@
         <v>9</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1952,22 +1952,22 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>8</v>
       </c>
       <c r="V16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>8</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1993,22 +1993,22 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2029,22 +2029,22 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U17">
         <v>8</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2070,22 +2070,22 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2106,22 +2106,22 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>7</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2147,22 +2147,22 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2183,7 +2183,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>9</v>
@@ -2195,10 +2195,10 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2224,22 +2224,22 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2260,7 +2260,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2272,10 +2272,10 @@
         <v>6</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2301,22 +2301,22 @@
         <v>7</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2337,10 +2337,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V21">
         <v>8</v>
@@ -2349,10 +2349,10 @@
         <v>6</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2378,22 +2378,22 @@
         <v>10</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2455,22 +2455,22 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2491,7 +2491,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2503,10 +2503,10 @@
         <v>7</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2532,22 +2532,22 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2568,7 +2568,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2580,10 +2580,10 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2609,22 +2609,22 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2645,22 +2645,22 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>9</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>9</v>
       </c>
       <c r="X25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2686,13 +2686,13 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -2701,7 +2701,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2722,13 +2722,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2737,7 +2737,7 @@
         <v>-1</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2763,22 +2763,22 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2811,7 +2811,7 @@
         <v>5</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2840,22 +2840,22 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2879,16 +2879,16 @@
         <v>9</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>6</v>
       </c>
       <c r="X28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y28">
         <v>9</v>
@@ -2917,22 +2917,22 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2953,10 +2953,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V29">
         <v>5</v>
@@ -2965,10 +2965,10 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2994,22 +2994,22 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3030,22 +3030,22 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
         <v>5</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3059,7 +3059,7 @@
         <v>9</v>
       </c>
       <c r="D31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E31">
         <v>10</v>
@@ -3071,22 +3071,22 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3110,10 +3110,10 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3148,22 +3148,22 @@
         <v>9</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3184,22 +3184,22 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>9</v>
       </c>
       <c r="V32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3225,22 +3225,22 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3261,22 +3261,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>9</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>9</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3302,22 +3302,22 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3338,10 +3338,10 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>7</v>
@@ -3350,10 +3350,10 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y34">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3379,22 +3379,22 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3415,7 +3415,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U35">
         <v>9</v>
@@ -3427,10 +3427,10 @@
         <v>8</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3456,22 +3456,22 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3492,22 +3492,22 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W36">
         <v>9</v>
       </c>
       <c r="X36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3533,22 +3533,22 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3569,7 +3569,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>8</v>
@@ -3581,10 +3581,10 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3610,22 +3610,22 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3646,7 +3646,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U38">
         <v>9</v>
@@ -3658,10 +3658,10 @@
         <v>9</v>
       </c>
       <c r="X38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3726,19 +3726,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>82.86</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G2">
-        <v>17.14</v>
+        <v>25.71</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3790,25 +3790,25 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3822,19 +3822,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>97.14</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="H5">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3914,7 +3914,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3949,10 +3949,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -3963,61 +3963,41 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>20330051920374</v>
+        <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920236</v>
+        <v>20330051920240</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920240</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
         <v>58</v>
       </c>
     </row>
@@ -4060,10 +4040,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -4071,16 +4051,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920374</v>
+        <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -4088,16 +4068,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920236</v>
+        <v>20330051920240</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -4105,30 +4085,30 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920240</v>
+        <v>20330051920187</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920187</v>
+        <v>20330051920220</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
         <v>126</v>
@@ -4139,13 +4119,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920220</v>
+        <v>20330051920374</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
         <v>127</v>
@@ -4159,10 +4139,10 @@
         <v>20330051920223</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
         <v>128</v>
@@ -4176,10 +4156,10 @@
         <v>20330051920224</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D9" t="s">
         <v>129</v>
@@ -4193,10 +4173,10 @@
         <v>20330051920225</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
         <v>130</v>
@@ -4210,10 +4190,10 @@
         <v>20330051920375</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
         <v>131</v>
@@ -4227,10 +4207,10 @@
         <v>20330051920226</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
         <v>132</v>
@@ -4244,10 +4224,10 @@
         <v>20330051920227</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D13" t="s">
         <v>133</v>
@@ -4261,10 +4241,10 @@
         <v>20330051920228</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D14" t="s">
         <v>134</v>
@@ -4278,10 +4258,10 @@
         <v>20330051920229</v>
       </c>
       <c r="B15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
         <v>135</v>
@@ -4295,10 +4275,10 @@
         <v>20330051920230</v>
       </c>
       <c r="B16" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
         <v>136</v>
@@ -4312,10 +4292,10 @@
         <v>20330051920231</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
         <v>137</v>
@@ -4329,10 +4309,10 @@
         <v>20330051920232</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
         <v>138</v>
@@ -4346,10 +4326,10 @@
         <v>20330051920233</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
         <v>139</v>
@@ -4363,10 +4343,10 @@
         <v>20330051920234</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
         <v>140</v>
@@ -4380,10 +4360,10 @@
         <v>20330051920376</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D21" t="s">
         <v>141</v>
@@ -4397,10 +4377,10 @@
         <v>20330051920237</v>
       </c>
       <c r="B22" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D22" t="s">
         <v>142</v>
@@ -4414,10 +4394,10 @@
         <v>20330051920238</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D23" t="s">
         <v>143</v>
@@ -4431,10 +4411,10 @@
         <v>20330051920239</v>
       </c>
       <c r="B24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D24" t="s">
         <v>144</v>
@@ -4448,10 +4428,10 @@
         <v>20330051920241</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -4465,10 +4445,10 @@
         <v>20330051920243</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -4482,10 +4462,10 @@
         <v>20330051920244</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
         <v>147</v>
@@ -4499,10 +4479,10 @@
         <v>20330051920248</v>
       </c>
       <c r="B28" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
         <v>148</v>
@@ -4516,10 +4496,10 @@
         <v>20330051920249</v>
       </c>
       <c r="B29" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
         <v>149</v>
@@ -4533,10 +4513,10 @@
         <v>20330051920250</v>
       </c>
       <c r="B30" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
         <v>150</v>
@@ -4550,10 +4530,10 @@
         <v>20330051920251</v>
       </c>
       <c r="B31" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
         <v>151</v>
@@ -4567,10 +4547,10 @@
         <v>20330051920252</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D32" t="s">
         <v>152</v>
@@ -4584,10 +4564,10 @@
         <v>20330051920253</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
         <v>153</v>
@@ -4601,10 +4581,10 @@
         <v>20330051920256</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C34" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D34" t="s">
         <v>154</v>
@@ -4618,10 +4598,10 @@
         <v>20330051920257</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D35" t="s">
         <v>155</v>
@@ -4635,10 +4615,10 @@
         <v>20330051920258</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D36" t="s">
         <v>156</v>
@@ -4654,7 +4634,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4686,16 +4666,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920374</v>
+        <v>20330051920237</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4709,39 +4689,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920374</v>
+        <v>20330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920237</v>
+        <v>20330051920240</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4755,45 +4735,45 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920237</v>
+        <v>20330051920240</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920251</v>
+        <v>20330051920241</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4801,22 +4781,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920251</v>
+        <v>20330051920241</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4824,45 +4804,45 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920221</v>
+        <v>20330051920244</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>112</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920228</v>
+        <v>20330051920244</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4870,45 +4850,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920240</v>
+        <v>20330051920251</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920243</v>
+        <v>20330051920251</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4916,24 +4896,93 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920244</v>
+        <v>20330051920221</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G12">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>20330051920374</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>20330051920228</v>
+      </c>
+      <c r="B14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>20330051920243</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCM - Estadisticos 20221.xlsx
+++ b/grupos/5ALCM - Estadisticos 20221.xlsx
@@ -1842,7 +1842,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1878,7 +1878,7 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V15">
         <v>5</v>

--- a/grupos/5ALCM - Estadisticos 20221.xlsx
+++ b/grupos/5ALCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -1001,7 +1001,7 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>9</v>
@@ -1078,7 +1078,7 @@
         <v>7</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1114,7 +1114,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>-1</v>
@@ -1155,7 +1155,7 @@
         <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
         <v>9</v>
@@ -1232,7 +1232,7 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
         <v>9</v>
@@ -1309,7 +1309,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1345,7 +1345,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1386,7 +1386,7 @@
         <v>7</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>9</v>
@@ -1463,7 +1463,7 @@
         <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>9</v>
@@ -1540,7 +1540,7 @@
         <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1617,7 +1617,7 @@
         <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -1653,7 +1653,7 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1694,7 +1694,7 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -1730,7 +1730,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1771,7 +1771,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
         <v>10</v>
@@ -1848,7 +1848,7 @@
         <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>9</v>
@@ -1925,7 +1925,7 @@
         <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -1961,7 +1961,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -2002,7 +2002,7 @@
         <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>9</v>
@@ -2079,7 +2079,7 @@
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -2156,7 +2156,7 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
         <v>9</v>
@@ -2233,7 +2233,7 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>9</v>
@@ -2310,7 +2310,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>9</v>
@@ -2387,7 +2387,7 @@
         <v>10</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L22">
         <v>9</v>
@@ -2464,7 +2464,7 @@
         <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -2500,7 +2500,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2541,7 +2541,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -2618,7 +2618,7 @@
         <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L25">
         <v>9</v>
@@ -2695,7 +2695,7 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2772,7 +2772,7 @@
         <v>5</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>9</v>
@@ -2849,7 +2849,7 @@
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L28">
         <v>9</v>
@@ -2885,7 +2885,7 @@
         <v>5</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2926,7 +2926,7 @@
         <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -3003,7 +3003,7 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>9</v>
@@ -3080,7 +3080,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -3157,7 +3157,7 @@
         <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -3234,7 +3234,7 @@
         <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>9</v>
@@ -3311,7 +3311,7 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L34">
         <v>9</v>
@@ -3388,7 +3388,7 @@
         <v>7</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>9</v>
@@ -3465,7 +3465,7 @@
         <v>8</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L36">
         <v>9</v>
@@ -3542,7 +3542,7 @@
         <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
         <v>9</v>
@@ -3578,7 +3578,7 @@
         <v>7</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>9</v>
@@ -3619,7 +3619,7 @@
         <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
         <v>9</v>
@@ -3758,19 +3758,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>88.56999999999999</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G3">
-        <v>11.43</v>
+        <v>14.29</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4634,7 +4634,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4758,22 +4758,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920241</v>
+        <v>20330051920244</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4781,22 +4781,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920241</v>
+        <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4804,16 +4804,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920244</v>
+        <v>20330051920251</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C8" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -4827,16 +4827,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920244</v>
+        <v>20330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C9" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -4850,45 +4850,45 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920251</v>
+        <v>20330051920221</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>120</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920251</v>
+        <v>20330051920374</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>151</v>
+        <v>127</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4896,39 +4896,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920221</v>
+        <v>20330051920228</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920374</v>
+        <v>20330051920243</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -4937,52 +4937,6 @@
         <v>56</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>20330051920228</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D14" t="s">
-        <v>134</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>20330051920243</v>
-      </c>
-      <c r="B15" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>146</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCM - Estadisticos 20221.xlsx
+++ b/grupos/5ALCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -194,12 +194,12 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
   </si>
   <si>
@@ -215,244 +215,244 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALVARADO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>ANGEL</t>
   </si>
   <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LASTRE</t>
+  </si>
+  <si>
+    <t>LARRINAGA</t>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>MARIANO</t>
+  </si>
+  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MACARIO</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMAN</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TLECUILE</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>CIRUELO</t>
+  </si>
+  <si>
     <t>MARIA</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>TEQUIHUATLE</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>GALEOTE</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>ENRIQUEZ</t>
+  </si>
+  <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>SANTES</t>
+  </si>
+  <si>
+    <t>MARINERO</t>
+  </si>
+  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>QUIAHUA</t>
+  </si>
+  <si>
+    <t>VALLEJO</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>VANELY JUDITH</t>
+  </si>
+  <si>
     <t>JOSSELIN GUADALUPE</t>
   </si>
   <si>
+    <t>JOSE ISAIAS</t>
+  </si>
+  <si>
+    <t>JENNIFER</t>
+  </si>
+  <si>
+    <t>FERNANDA</t>
+  </si>
+  <si>
+    <t>JUAN ALBERTO</t>
+  </si>
+  <si>
+    <t>JENIFER</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>VICTORINO</t>
+  </si>
+  <si>
+    <t>GERMAN ISAI</t>
+  </si>
+  <si>
+    <t>MARIA ISABEL</t>
+  </si>
+  <si>
+    <t>ARTURO</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>EVELYN</t>
+  </si>
+  <si>
+    <t>ATENEA</t>
+  </si>
+  <si>
+    <t>GONZALO FEDERICO</t>
+  </si>
+  <si>
+    <t>MERARY MADAY</t>
+  </si>
+  <si>
     <t>GENARO RAFAEL</t>
   </si>
   <si>
+    <t>JACQUELINE</t>
+  </si>
+  <si>
+    <t>CAROLINA</t>
+  </si>
+  <si>
+    <t>PERLA MARITZA</t>
+  </si>
+  <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LASTRE</t>
-  </si>
-  <si>
-    <t>LARRINAGA</t>
-  </si>
-  <si>
-    <t>LIMA</t>
-  </si>
-  <si>
-    <t>MARIANO</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TLECUILE</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>CIRUELO</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>TEQUIHUATLE</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>GALEOTE</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>ENRIQUEZ</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>SANTES</t>
-  </si>
-  <si>
-    <t>MARINERO</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>VALLEJO</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>VANELY JUDITH</t>
-  </si>
-  <si>
-    <t>JOSE ISAIAS</t>
-  </si>
-  <si>
-    <t>JENNIFER</t>
-  </si>
-  <si>
-    <t>FERNANDA</t>
-  </si>
-  <si>
-    <t>JUAN ALBERTO</t>
-  </si>
-  <si>
-    <t>JENIFER</t>
-  </si>
-  <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>VICTORINO</t>
-  </si>
-  <si>
-    <t>GERMAN ISAI</t>
-  </si>
-  <si>
-    <t>MARIA ISABEL</t>
-  </si>
-  <si>
-    <t>ARTURO</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
-  </si>
-  <si>
-    <t>ATENEA</t>
-  </si>
-  <si>
-    <t>GONZALO FEDERICO</t>
-  </si>
-  <si>
-    <t>MERARY MADAY</t>
-  </si>
-  <si>
-    <t>JACQUELINE</t>
-  </si>
-  <si>
-    <t>CAROLINA</t>
-  </si>
-  <si>
-    <t>PERLA MARITZA</t>
   </si>
   <si>
     <t>ITZEL</t>
@@ -1063,7 +1063,7 @@
         <v>6</v>
       </c>
       <c r="F5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G5">
         <v>7</v>
@@ -1081,7 +1081,7 @@
         <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>8</v>
@@ -1117,7 +1117,7 @@
         <v>7</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>8</v>
@@ -2680,7 +2680,7 @@
         <v>8</v>
       </c>
       <c r="F26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G26">
         <v>9</v>
@@ -2698,7 +2698,7 @@
         <v>8</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M26">
         <v>10</v>
@@ -2734,7 +2734,7 @@
         <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
         <v>10</v>
@@ -2748,7 +2748,7 @@
         <v>8</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -2766,7 +2766,7 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
         <v>5</v>
@@ -2802,7 +2802,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3793,27 +3793,27 @@
         <v>33</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>94.29000000000001</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>5.71</v>
       </c>
       <c r="H4">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="I4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3822,25 +3822,25 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3914,7 +3914,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3939,66 +3939,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920221</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920236</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920240</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4034,64 +3974,64 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920221</v>
+        <v>20330051920187</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920236</v>
+        <v>20330051920220</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920240</v>
+        <v>20330051920221</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920187</v>
+        <v>20330051920374</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
         <v>125</v>
@@ -4102,13 +4042,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920220</v>
+        <v>20330051920223</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
         <v>126</v>
@@ -4119,13 +4059,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920374</v>
+        <v>20330051920224</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>127</v>
@@ -4136,13 +4076,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920223</v>
+        <v>20330051920225</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>128</v>
@@ -4153,13 +4093,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920224</v>
+        <v>20330051920375</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
         <v>129</v>
@@ -4170,13 +4110,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920225</v>
+        <v>20330051920226</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
         <v>130</v>
@@ -4187,13 +4127,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920375</v>
+        <v>20330051920227</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
         <v>131</v>
@@ -4204,13 +4144,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920226</v>
+        <v>20330051920228</v>
       </c>
       <c r="B12" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
         <v>132</v>
@@ -4221,13 +4161,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920227</v>
+        <v>20330051920229</v>
       </c>
       <c r="B13" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D13" t="s">
         <v>133</v>
@@ -4238,13 +4178,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920228</v>
+        <v>20330051920230</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D14" t="s">
         <v>134</v>
@@ -4255,13 +4195,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920229</v>
+        <v>20330051920231</v>
       </c>
       <c r="B15" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D15" t="s">
         <v>135</v>
@@ -4272,13 +4212,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920230</v>
+        <v>20330051920232</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
         <v>136</v>
@@ -4289,13 +4229,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920231</v>
+        <v>20330051920233</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
         <v>137</v>
@@ -4306,13 +4246,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920232</v>
+        <v>20330051920234</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
         <v>138</v>
@@ -4323,13 +4263,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920233</v>
+        <v>20330051920376</v>
       </c>
       <c r="B19" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D19" t="s">
         <v>139</v>
@@ -4340,13 +4280,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920234</v>
+        <v>20330051920236</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C20" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D20" t="s">
         <v>140</v>
@@ -4357,13 +4297,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920376</v>
+        <v>20330051920237</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
         <v>141</v>
@@ -4374,13 +4314,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920237</v>
+        <v>20330051920238</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
         <v>142</v>
@@ -4391,13 +4331,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920238</v>
+        <v>20330051920239</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="D23" t="s">
         <v>143</v>
@@ -4408,13 +4348,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920239</v>
+        <v>20330051920240</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
         <v>144</v>
@@ -4428,10 +4368,10 @@
         <v>20330051920241</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C25" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
         <v>145</v>
@@ -4445,10 +4385,10 @@
         <v>20330051920243</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="D26" t="s">
         <v>146</v>
@@ -4462,10 +4402,10 @@
         <v>20330051920244</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D27" t="s">
         <v>147</v>
@@ -4479,10 +4419,10 @@
         <v>20330051920248</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C28" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
         <v>148</v>
@@ -4496,10 +4436,10 @@
         <v>20330051920249</v>
       </c>
       <c r="B29" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
         <v>149</v>
@@ -4513,10 +4453,10 @@
         <v>20330051920250</v>
       </c>
       <c r="B30" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D30" t="s">
         <v>150</v>
@@ -4530,10 +4470,10 @@
         <v>20330051920251</v>
       </c>
       <c r="B31" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D31" t="s">
         <v>151</v>
@@ -4547,10 +4487,10 @@
         <v>20330051920252</v>
       </c>
       <c r="B32" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D32" t="s">
         <v>152</v>
@@ -4564,10 +4504,10 @@
         <v>20330051920253</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D33" t="s">
         <v>153</v>
@@ -4581,10 +4521,10 @@
         <v>20330051920256</v>
       </c>
       <c r="B34" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C34" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D34" t="s">
         <v>154</v>
@@ -4598,10 +4538,10 @@
         <v>20330051920257</v>
       </c>
       <c r="B35" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D35" t="s">
         <v>155</v>
@@ -4615,10 +4555,10 @@
         <v>20330051920258</v>
       </c>
       <c r="B36" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D36" t="s">
         <v>156</v>
@@ -4634,7 +4574,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4669,13 +4609,13 @@
         <v>20330051920237</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -4692,13 +4632,13 @@
         <v>20330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4712,16 +4652,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920240</v>
+        <v>20330051920244</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4735,39 +4675,39 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920240</v>
+        <v>20330051920244</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>147</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920244</v>
+        <v>20330051920251</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -4781,16 +4721,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920244</v>
+        <v>20330051920251</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D7" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -4804,16 +4744,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920251</v>
+        <v>20330051920374</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>125</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
@@ -4827,22 +4767,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920251</v>
+        <v>20330051920228</v>
       </c>
       <c r="B9" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4850,39 +4790,39 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920221</v>
+        <v>20330051920240</v>
       </c>
       <c r="B10" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920374</v>
+        <v>20330051920243</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>127</v>
+        <v>146</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -4891,52 +4831,6 @@
         <v>56</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>20330051920228</v>
-      </c>
-      <c r="B12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" t="s">
-        <v>134</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920243</v>
-      </c>
-      <c r="B13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>146</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCM - Estadisticos 20221.xlsx
+++ b/grupos/5ALCM - Estadisticos 20221.xlsx
@@ -1010,7 +1010,7 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -1025,7 +1025,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -1087,7 +1087,7 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -1102,7 +1102,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>8</v>
@@ -1164,7 +1164,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1179,7 +1179,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>8</v>
@@ -1241,7 +1241,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1256,7 +1256,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1318,7 +1318,7 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1333,7 +1333,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1395,7 +1395,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1410,10 +1410,10 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1428,7 +1428,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1472,7 +1472,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1487,7 +1487,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1549,7 +1549,7 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1564,10 +1564,10 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1582,7 +1582,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1626,7 +1626,7 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1641,10 +1641,10 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>7</v>
@@ -1659,7 +1659,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1703,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1718,7 +1718,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1780,7 +1780,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1795,7 +1795,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1857,7 +1857,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1872,7 +1872,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -1934,7 +1934,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1949,7 +1949,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -2011,7 +2011,7 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -2026,7 +2026,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
         <v>8</v>
@@ -2088,7 +2088,7 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -2103,7 +2103,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2165,7 +2165,7 @@
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
         <v>-1</v>
@@ -2180,7 +2180,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -2242,7 +2242,7 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O20">
         <v>-1</v>
@@ -2257,10 +2257,10 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2275,7 +2275,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2319,7 +2319,7 @@
         <v>8</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>-1</v>
@@ -2334,7 +2334,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2396,7 +2396,7 @@
         <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>-1</v>
@@ -2411,7 +2411,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>10</v>
@@ -2473,7 +2473,7 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
         <v>-1</v>
@@ -2488,7 +2488,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2506,7 +2506,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2550,7 +2550,7 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O24">
         <v>-1</v>
@@ -2565,10 +2565,10 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U24">
         <v>7</v>
@@ -2583,7 +2583,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2627,7 +2627,7 @@
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
         <v>-1</v>
@@ -2642,7 +2642,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>-1</v>
@@ -2719,7 +2719,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
         <v>10</v>
@@ -2781,7 +2781,7 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>-1</v>
@@ -2796,7 +2796,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T27">
         <v>8</v>
@@ -2858,7 +2858,7 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
         <v>-1</v>
@@ -2873,10 +2873,10 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -2891,7 +2891,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2935,7 +2935,7 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>-1</v>
@@ -2950,7 +2950,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -3012,7 +3012,7 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>-1</v>
@@ -3027,10 +3027,10 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3045,7 +3045,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3089,7 +3089,7 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
         <v>-1</v>
@@ -3104,7 +3104,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3166,7 +3166,7 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
         <v>-1</v>
@@ -3181,7 +3181,7 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3243,7 +3243,7 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
@@ -3258,7 +3258,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3320,7 +3320,7 @@
         <v>8</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O34">
         <v>-1</v>
@@ -3335,7 +3335,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>8</v>
@@ -3397,7 +3397,7 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O35">
         <v>-1</v>
@@ -3412,7 +3412,7 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>9</v>
@@ -3474,7 +3474,7 @@
         <v>8</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>-1</v>
@@ -3489,7 +3489,7 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3551,7 +3551,7 @@
         <v>9</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>-1</v>
@@ -3566,7 +3566,7 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -3628,7 +3628,7 @@
         <v>9</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O38">
         <v>-1</v>
@@ -3643,7 +3643,7 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3898,7 +3898,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/5ALCM - Estadisticos 20221.xlsx
+++ b/grupos/5ALCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -188,16 +188,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Ortega Valle Manuel</t>
   </si>
   <si>
-    <t>González Sánchez Rene Aurelio</t>
+    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
     <t>Ángel Martínez Gerson Hermenegildo</t>
@@ -1013,16 +1013,16 @@
         <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S4">
         <v>10</v>
@@ -1090,16 +1090,16 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
         <v>10</v>
@@ -1167,16 +1167,16 @@
         <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -1244,16 +1244,16 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
         <v>10</v>
@@ -1265,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1321,16 +1321,16 @@
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>9</v>
@@ -1339,7 +1339,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1398,16 +1398,16 @@
         <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S9">
         <v>8</v>
@@ -1475,16 +1475,16 @@
         <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>8</v>
@@ -1493,7 +1493,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1552,16 +1552,16 @@
         <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>6</v>
@@ -1629,16 +1629,16 @@
         <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -1706,16 +1706,16 @@
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
         <v>9</v>
@@ -1783,16 +1783,16 @@
         <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>10</v>
@@ -1860,16 +1860,16 @@
         <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>10</v>
@@ -1881,7 +1881,7 @@
         <v>8</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>7</v>
@@ -1937,16 +1937,16 @@
         <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -2014,16 +2014,16 @@
         <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>9</v>
@@ -2091,16 +2091,16 @@
         <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
         <v>9</v>
@@ -2109,7 +2109,7 @@
         <v>9</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2168,16 +2168,16 @@
         <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
         <v>10</v>
@@ -2245,16 +2245,16 @@
         <v>6</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>7</v>
@@ -2263,7 +2263,7 @@
         <v>8</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>7</v>
@@ -2322,16 +2322,16 @@
         <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>9</v>
@@ -2399,16 +2399,16 @@
         <v>10</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>10</v>
@@ -2476,16 +2476,16 @@
         <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>8</v>
@@ -2494,7 +2494,7 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>7</v>
@@ -2553,16 +2553,16 @@
         <v>7</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>7</v>
@@ -2630,16 +2630,16 @@
         <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
         <v>10</v>
@@ -2648,7 +2648,7 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>9</v>
@@ -2707,16 +2707,16 @@
         <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>10</v>
@@ -2728,7 +2728,7 @@
         <v>8</v>
       </c>
       <c r="V26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2784,16 +2784,16 @@
         <v>7</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>7</v>
@@ -2802,7 +2802,7 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>5</v>
@@ -2861,16 +2861,16 @@
         <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
         <v>7</v>
@@ -2879,10 +2879,10 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>5</v>
@@ -2938,16 +2938,16 @@
         <v>8</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
         <v>8</v>
@@ -2959,7 +2959,7 @@
         <v>8</v>
       </c>
       <c r="V29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>8</v>
@@ -3015,16 +3015,16 @@
         <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
         <v>6</v>
@@ -3033,7 +3033,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>5</v>
@@ -3092,16 +3092,16 @@
         <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
         <v>10</v>
@@ -3110,7 +3110,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
         <v>10</v>
@@ -3169,16 +3169,16 @@
         <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
         <v>10</v>
@@ -3246,16 +3246,16 @@
         <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>9</v>
@@ -3323,16 +3323,16 @@
         <v>9</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>9</v>
@@ -3400,16 +3400,16 @@
         <v>9</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>9</v>
@@ -3477,16 +3477,16 @@
         <v>10</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S36">
         <v>10</v>
@@ -3554,16 +3554,16 @@
         <v>10</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
         <v>10</v>
@@ -3631,16 +3631,16 @@
         <v>9</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S38">
         <v>9</v>
@@ -3649,7 +3649,7 @@
         <v>9</v>
       </c>
       <c r="U38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>8</v>
@@ -3717,7 +3717,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -3726,19 +3726,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>74.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G2">
-        <v>25.71</v>
+        <v>14.29</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3758,19 +3758,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>85.70999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G3">
-        <v>14.29</v>
+        <v>11.43</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3781,7 +3781,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3790,19 +3790,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4574,7 +4574,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4606,22 +4606,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920237</v>
+        <v>20330051920236</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920237</v>
+        <v>20330051920236</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4652,22 +4652,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920244</v>
+        <v>20330051920237</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4675,22 +4675,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920244</v>
+        <v>20330051920237</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4698,22 +4698,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920251</v>
+        <v>20330051920244</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4721,22 +4721,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920251</v>
+        <v>20330051920244</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920374</v>
+        <v>20330051920251</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="E8" t="s">
         <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4767,19 +4767,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920228</v>
+        <v>20330051920251</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
         <v>56</v>
@@ -4790,47 +4790,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920240</v>
+        <v>20330051920241</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>20330051920243</v>
-      </c>
-      <c r="B11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C11" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" t="s">
-        <v>146</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-      <c r="G11">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCM - Estadisticos 20221.xlsx
+++ b/grupos/5ALCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="157">
   <si>
     <t>Materia</t>
   </si>
@@ -188,10 +188,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ortega Valle Manuel</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Ortega Valle Manuel</t>
   </si>
   <si>
     <t>Pesce Bautista Victor Manuel</t>
@@ -1019,7 +1019,7 @@
         <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>9</v>
@@ -1096,7 +1096,7 @@
         <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R5">
         <v>9</v>
@@ -1114,7 +1114,7 @@
         <v>7</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>8</v>
@@ -1173,7 +1173,7 @@
         <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>9</v>
@@ -1191,7 +1191,7 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1250,7 +1250,7 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
         <v>9</v>
@@ -1327,7 +1327,7 @@
         <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>9</v>
@@ -1345,7 +1345,7 @@
         <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1404,7 +1404,7 @@
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>9</v>
@@ -1422,7 +1422,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1481,7 +1481,7 @@
         <v>8</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R10">
         <v>9</v>
@@ -1558,7 +1558,7 @@
         <v>5</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>9</v>
@@ -1635,7 +1635,7 @@
         <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>9</v>
@@ -1653,7 +1653,7 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1712,7 +1712,7 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>9</v>
@@ -1730,7 +1730,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1789,7 +1789,7 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>10</v>
@@ -1866,7 +1866,7 @@
         <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>9</v>
@@ -1884,7 +1884,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>9</v>
@@ -1943,7 +1943,7 @@
         <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>10</v>
@@ -2020,7 +2020,7 @@
         <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
         <v>9</v>
@@ -2038,7 +2038,7 @@
         <v>7</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>9</v>
@@ -2097,7 +2097,7 @@
         <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>9</v>
@@ -2174,7 +2174,7 @@
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>9</v>
@@ -2192,7 +2192,7 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2251,7 +2251,7 @@
         <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R20">
         <v>9</v>
@@ -2328,7 +2328,7 @@
         <v>9</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>9</v>
@@ -2346,7 +2346,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2405,7 +2405,7 @@
         <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>10</v>
@@ -2482,7 +2482,7 @@
         <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>9</v>
@@ -2500,7 +2500,7 @@
         <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2559,7 +2559,7 @@
         <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -2636,7 +2636,7 @@
         <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>9</v>
@@ -2713,7 +2713,7 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -2731,7 +2731,7 @@
         <v>6</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
         <v>8</v>
@@ -2790,7 +2790,7 @@
         <v>5</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>9</v>
@@ -2808,7 +2808,7 @@
         <v>5</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2867,7 +2867,7 @@
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>9</v>
@@ -2885,7 +2885,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2944,7 +2944,7 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>9</v>
@@ -2962,7 +2962,7 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X29">
         <v>9</v>
@@ -3021,7 +3021,7 @@
         <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
         <v>9</v>
@@ -3039,7 +3039,7 @@
         <v>5</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -3098,7 +3098,7 @@
         <v>10</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>9</v>
@@ -3175,7 +3175,7 @@
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>9</v>
@@ -3252,7 +3252,7 @@
         <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>9</v>
@@ -3270,7 +3270,7 @@
         <v>8</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>8</v>
@@ -3329,7 +3329,7 @@
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
         <v>9</v>
@@ -3406,7 +3406,7 @@
         <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>9</v>
@@ -3483,7 +3483,7 @@
         <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>9</v>
@@ -3560,7 +3560,7 @@
         <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>9</v>
@@ -3637,7 +3637,7 @@
         <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>9</v>
@@ -3717,7 +3717,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -3726,19 +3726,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>85.70999999999999</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G2">
-        <v>14.29</v>
+        <v>11.43</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3749,7 +3749,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3758,19 +3758,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>88.56999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G3">
-        <v>11.43</v>
+        <v>5.71</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4574,7 +4574,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4606,22 +4606,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920236</v>
+        <v>20330051920237</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920236</v>
+        <v>20330051920237</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4652,22 +4652,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920237</v>
+        <v>20330051920251</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4675,22 +4675,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920237</v>
+        <v>20330051920251</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D5" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4698,22 +4698,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920244</v>
+        <v>20330051920236</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D6" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4733,81 +4733,12 @@
         <v>147</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
         <v>56</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920251</v>
-      </c>
-      <c r="B8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" t="s">
-        <v>117</v>
-      </c>
-      <c r="D8" t="s">
-        <v>151</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920251</v>
-      </c>
-      <c r="B9" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" t="s">
-        <v>117</v>
-      </c>
-      <c r="D9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>56</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920241</v>
-      </c>
-      <c r="B10" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" t="s">
-        <v>115</v>
-      </c>
-      <c r="D10" t="s">
-        <v>145</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>
